--- a/1-运维服务目录/TXHS-01-02-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/TXHS-01-02-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="28515" windowHeight="12315" tabRatio="751" firstSheet="23" activeTab="28"/>
+    <workbookView windowWidth="22188" windowHeight="9575" tabRatio="751" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="修订页" sheetId="68" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <definedName name="针对质监行业领域的应用软件优化改善服务">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">修订页!$A$5:$H$14</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="324">
   <si>
     <t>桐乡华数广电网络有限公司</t>
   </si>
@@ -109,13 +109,13 @@
     <t>V1.0</t>
   </si>
   <si>
-    <t>强宇涛</t>
+    <t>程方</t>
   </si>
   <si>
     <t>2025.1.11</t>
   </si>
   <si>
-    <t>陈凯</t>
+    <t>茅建根</t>
   </si>
   <si>
     <t>吴亚红</t>
@@ -461,7 +461,7 @@
     <t>应用软件例行操作服务</t>
   </si>
   <si>
-    <t>对管理系统的运行情况进行实时监控、检查、例行维护服务</t>
+    <t>对视频管理系统的运行情况进行实时监控、检查、例行维护服务</t>
   </si>
   <si>
     <t>0403030102</t>
@@ -470,7 +470,7 @@
     <t>应用软件响应支持服务</t>
   </si>
   <si>
-    <t>对使用管理系统的用户所提出的软件请求，以及系统故障进行及时的响应和处理</t>
+    <t>对使用视频管理系统的用户所提出的软件请求，以及系统故障进行及时的响应和处理</t>
   </si>
   <si>
     <t>0403030103</t>
@@ -479,7 +479,7 @@
     <t>应用软件优化改善服务</t>
   </si>
   <si>
-    <t>针对应用软件的系统运行情况，给出优化建议并实施，提升性能。</t>
+    <t>针对视频管理系统的系统运行情况，给出优化建议并实施，提升性能。</t>
   </si>
   <si>
     <t>0403030104</t>
@@ -488,7 +488,7 @@
     <t>应用软件调研评估服务</t>
   </si>
   <si>
-    <t>对目前运行的应用软件进行多方面的测试，并提供相应的性能评估</t>
+    <t>对目前运行的视频管理系统进行多方面的测试，并提供相应的性能评估</t>
   </si>
   <si>
     <t>0402010101交换机例行操作服务</t>
@@ -1354,7 +1354,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1366,7 +1365,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1377,7 +1375,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1388,7 +1385,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1400,7 +1396,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1411,7 +1406,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1423,7 +1417,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1434,7 +1427,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1446,7 +1438,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1457,7 +1448,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1469,7 +1459,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1480,7 +1469,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1492,7 +1480,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1503,7 +1490,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1514,7 +1500,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1526,7 +1511,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1537,7 +1521,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1549,7 +1532,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1560,7 +1542,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1571,7 +1552,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1582,7 +1562,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1594,7 +1573,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1605,7 +1583,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1617,7 +1594,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1628,7 +1604,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1640,7 +1615,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1651,7 +1625,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1663,7 +1636,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1674,7 +1646,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1686,7 +1657,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1697,7 +1667,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1709,7 +1678,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1720,7 +1688,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1732,7 +1699,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1743,7 +1709,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1762,7 +1727,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>0403010</t>
@@ -1772,7 +1736,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -1782,7 +1745,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
@@ -1823,7 +1785,7 @@
     <t>04030301-应用软件运维服务</t>
   </si>
   <si>
-    <t>对管理系统的运行情况进行实时检查</t>
+    <t>对视频监控系统的运行情况进行实时检查</t>
   </si>
   <si>
     <t>确保管理系统运行正常，及时发现问题，保证机构能正常使用系统办理相关业务。</t>
@@ -1863,7 +1825,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -1873,14 +1834,13 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>-应用软件运维服务</t>
     </r>
   </si>
   <si>
-    <t>对使用管理系统的用户所提出的软件故障进行及时的响应和处理</t>
+    <t>对使用视频监控系统的用户所提出的软件故障进行及时的响应和处理</t>
   </si>
   <si>
     <t>对用户的故障请求，及时响应，分析诊断问题，尽快的排除故障，保证机构能正常使用系统办理相关业务。</t>
@@ -1940,7 +1900,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -1950,14 +1909,16 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
     </r>
   </si>
   <si>
-    <t>从多方面对应用软件进行评估，确保应用软件的高可用高性能及稳定性，为客户提供系统优化升级改进等技术服务。</t>
+    <t>对目前运行的应用软件进行多方面的测试，并提供相应的性能评估</t>
+  </si>
+  <si>
+    <t>从多方面对视频监控系统进行评估，确保应用软件的高可用高性能及稳定性，为客户提供系统优化升级改进等技术服务。</t>
   </si>
   <si>
     <t>按客户要求对应用软件进行评估，保证应用软件能平稳运行，具体评估内容如下：
@@ -1980,25 +1941,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2006,14 +1960,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2021,7 +1973,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2029,7 +1980,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2037,14 +1987,12 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2052,26 +2000,22 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2079,14 +2023,12 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2094,13 +2036,11 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2108,7 +2048,6 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2117,7 +2056,6 @@
       <sz val="24"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2125,38 +2063,40 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="楷体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="楷体_GB2312"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u val="single"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2164,7 +2104,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2173,7 +2112,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2182,7 +2120,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2191,7 +2128,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2200,7 +2136,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2209,7 +2144,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2217,7 +2151,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2226,7 +2159,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2235,7 +2167,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2244,7 +2175,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2252,7 +2182,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2260,7 +2189,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2268,7 +2196,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2276,7 +2203,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2284,25 +2210,40 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2490,18 +2431,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -2509,6 +2438,93 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2524,6 +2540,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2532,6 +2549,7 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2540,6 +2558,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2554,6 +2573,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2568,6 +2588,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -2582,6 +2603,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2590,6 +2612,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2600,691 +2623,403 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="80">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="62">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="13" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="72">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="66">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
-    <cellStyle name="千位分隔" xfId="20"/>
-    <cellStyle name="货币" xfId="21"/>
-    <cellStyle name="百分比" xfId="22"/>
-    <cellStyle name="千位分隔[0]" xfId="23"/>
-    <cellStyle name="货币[0]" xfId="24"/>
-    <cellStyle name="超链接" xfId="25"/>
-    <cellStyle name="已访问的超链接" xfId="26"/>
-    <cellStyle name="注释" xfId="27"/>
-    <cellStyle name="警告文本" xfId="28"/>
-    <cellStyle name="标题" xfId="29"/>
-    <cellStyle name="解释性文本" xfId="30"/>
-    <cellStyle name="标题 1" xfId="31"/>
-    <cellStyle name="标题 2" xfId="32"/>
-    <cellStyle name="标题 3" xfId="33"/>
-    <cellStyle name="标题 4" xfId="34"/>
-    <cellStyle name="输入" xfId="35"/>
-    <cellStyle name="输出" xfId="36"/>
-    <cellStyle name="计算" xfId="37"/>
-    <cellStyle name="检查单元格" xfId="38"/>
-    <cellStyle name="链接单元格" xfId="39"/>
-    <cellStyle name="汇总" xfId="40"/>
-    <cellStyle name="好" xfId="41"/>
-    <cellStyle name="差" xfId="42"/>
-    <cellStyle name="适中" xfId="43"/>
-    <cellStyle name="强调文字颜色 1" xfId="44"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
-    <cellStyle name="强调文字颜色 2" xfId="48"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
-    <cellStyle name="强调文字颜色 3" xfId="52"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
-    <cellStyle name="强调文字颜色 4" xfId="56"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
-    <cellStyle name="强调文字颜色 5" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
-    <cellStyle name="强调文字颜色 6" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
-    <cellStyle name="Percent" xfId="68"/>
-    <cellStyle name="Currency" xfId="69"/>
-    <cellStyle name="Currency [0]" xfId="70"/>
-    <cellStyle name="Comma" xfId="71"/>
-    <cellStyle name="Comma [0]" xfId="72"/>
-    <cellStyle name="常规 2 2 4" xfId="73"/>
-    <cellStyle name="常规 2 2 2" xfId="74"/>
-    <cellStyle name="常规 2 2 3" xfId="75"/>
-    <cellStyle name="常规 2 2" xfId="76"/>
-    <cellStyle name="常规 2" xfId="77"/>
-    <cellStyle name="常规 3" xfId="78"/>
-    <cellStyle name="常规 4" xfId="79"/>
+  <cellStyles count="62">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="Percent" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="Currency [0]" xfId="52"/>
+    <cellStyle name="Comma" xfId="53"/>
+    <cellStyle name="Comma [0]" xfId="54"/>
+    <cellStyle name="常规 2 2 4" xfId="55"/>
+    <cellStyle name="常规 2 2 2" xfId="56"/>
+    <cellStyle name="常规 2 2 3" xfId="57"/>
+    <cellStyle name="常规 2 2" xfId="58"/>
+    <cellStyle name="常规 2" xfId="59"/>
+    <cellStyle name="常规 3" xfId="60"/>
+    <cellStyle name="常规 4" xfId="61"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3579,281 +3314,281 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.125" customWidth="1"/>
-    <col min="2" max="2" width="7.625" customWidth="1"/>
-    <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="1" max="1" width="6.12962962962963" customWidth="1"/>
+    <col min="2" max="2" width="7.62962962962963" customWidth="1"/>
+    <col min="3" max="3" width="9.87962962962963" customWidth="1"/>
+    <col min="4" max="4" width="12.8796296296296" customWidth="1"/>
+    <col min="5" max="5" width="14.1296296296296" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="12.75" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.1" customHeight="1"/>
-    <row r="2" spans="1:9" ht="13.5"/>
-    <row r="3" spans="1:9" ht="13.5">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-    </row>
-    <row r="4" spans="1:9" ht="13.5">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-    </row>
-    <row r="5" spans="1:9" ht="27" customHeight="1">
-      <c r="A5" s="66" t="s">
+    <row r="1" ht="14.1" customHeight="1"/>
+    <row r="3" spans="1:9">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+    </row>
+    <row r="5" ht="27" customHeight="1" spans="1:9">
+      <c r="A5" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-    </row>
-    <row r="6" spans="1:9" ht="48" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:9">
+      <c r="A6" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.5">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="68" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-    </row>
-    <row r="8" spans="1:9" ht="13.5">
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-    </row>
-    <row r="9" spans="1:9" ht="21" customHeight="1">
-      <c r="A9" s="69" t="s">
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+    </row>
+    <row r="9" ht="21" customHeight="1" spans="1:9">
+      <c r="A9" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-    </row>
-    <row r="10" spans="1:9" ht="13.5">
-      <c r="A10" s="70" t="s">
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="71" t="s">
+      <c r="G10" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="71" t="s">
+      <c r="H10" s="68" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="13.5">
-      <c r="A11" s="72"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+    <row r="11" spans="1:9">
+      <c r="A11" s="69"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
       <c r="I11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="35.1" customHeight="1">
-      <c r="A12" s="24">
+    <row r="12" ht="35.1" customHeight="1" spans="1:9">
+      <c r="A12" s="23">
         <v>1</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="74" t="s">
+      <c r="E12" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="74" t="s">
+      <c r="F12" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="74" t="s">
+      <c r="G12" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="74" t="s">
+      <c r="H12" s="71" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30.9" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-    </row>
-    <row r="14" spans="1:8" ht="30.9" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-    </row>
-    <row r="15" spans="1:8" ht="28" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16" spans="1:8" ht="33" customHeight="1">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-    </row>
-    <row r="17" spans="1:8" ht="27" customHeight="1">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-    </row>
-    <row r="20" spans="2:7" ht="13.5">
-      <c r="B20" s="65"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-    </row>
-    <row r="21" spans="2:7" ht="13.5">
-      <c r="B21" s="65"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-    </row>
-    <row r="22" spans="2:7" ht="13.5">
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-    </row>
-    <row r="23" spans="2:7" ht="13.5">
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-    </row>
-    <row r="24" spans="2:7" ht="13.5">
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-    </row>
-    <row r="25" spans="2:7" ht="13.5">
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-    </row>
-    <row r="26" spans="2:7" ht="13.5">
-      <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-    </row>
-    <row r="27" spans="2:7" ht="13.5">
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-    </row>
-    <row r="28" spans="2:7" ht="13.5">
-      <c r="B28" s="65"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
+    <row r="13" ht="30.9" customHeight="1" spans="1:9">
+      <c r="A13" s="23"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+    </row>
+    <row r="14" ht="30.9" customHeight="1" spans="1:9">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:9">
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" ht="33" customHeight="1" spans="1:9">
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+    </row>
+    <row r="17" ht="27" customHeight="1" spans="1:8">
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3870,27 +3605,29 @@
     <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.0784722222222222" right="0.314583333333333" top="0.75" bottom="0.75" header="0.393055555555556" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -3898,7 +3635,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -3906,31 +3643,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -3938,7 +3675,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -3946,7 +3683,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -3954,13 +3691,13 @@
         <v>201</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -3968,7 +3705,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="378">
+    <row r="12" ht="403.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -3976,7 +3713,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -3984,7 +3721,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -3992,7 +3729,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4000,7 +3737,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4014,27 +3751,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4042,7 +3781,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4050,31 +3789,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4082,7 +3821,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4090,7 +3829,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4098,13 +3837,13 @@
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4112,7 +3851,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="297">
+    <row r="12" ht="316.8" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4120,7 +3859,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4128,7 +3867,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -4136,7 +3875,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4144,7 +3883,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4158,27 +3897,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="69" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="69" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4186,7 +3927,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4194,31 +3935,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4226,7 +3967,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4234,7 +3975,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4242,13 +3983,13 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4256,7 +3997,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="256.5">
+    <row r="12" ht="273.6" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4264,7 +4005,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4272,7 +4013,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -4280,7 +4021,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4288,7 +4029,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4302,27 +4043,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4330,7 +4073,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4338,31 +4081,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4370,7 +4113,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4378,7 +4121,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4386,13 +4129,13 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4400,7 +4143,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="256.5">
+    <row r="12" ht="273.6" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4408,7 +4151,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4416,7 +4159,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -4424,7 +4167,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4432,7 +4175,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4446,27 +4189,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4474,7 +4219,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4482,31 +4227,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4514,7 +4259,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4522,7 +4267,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4530,13 +4275,13 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4544,7 +4289,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="310.5">
+    <row r="12" ht="331.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4552,7 +4297,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4560,7 +4305,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -4568,7 +4313,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4576,7 +4321,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4590,27 +4335,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4618,7 +4365,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4626,31 +4373,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4658,7 +4405,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4666,7 +4413,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4674,13 +4421,13 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4688,7 +4435,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="216">
+    <row r="12" ht="230.4" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4696,7 +4443,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4704,7 +4451,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -4712,7 +4459,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4720,7 +4467,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4734,27 +4481,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4762,7 +4511,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4770,31 +4519,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4802,7 +4551,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4810,7 +4559,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4818,13 +4567,13 @@
         <v>236</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4832,7 +4581,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="283.5">
+    <row r="12" ht="302.4" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4840,7 +4589,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4848,7 +4597,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -4856,7 +4605,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -4864,7 +4613,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -4878,27 +4627,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -4906,7 +4657,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -4914,31 +4665,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -4946,7 +4697,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -4954,7 +4705,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -4962,13 +4713,13 @@
         <v>241</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -4976,7 +4727,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="256.5">
+    <row r="12" ht="273.6" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -4984,7 +4735,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -4992,7 +4743,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -5000,7 +4751,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -5008,7 +4759,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -5022,27 +4773,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -5050,7 +4803,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -5058,31 +4811,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -5090,7 +4843,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -5098,7 +4851,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -5106,13 +4859,13 @@
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -5120,7 +4873,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="297">
+    <row r="12" ht="316.8" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -5128,7 +4881,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -5136,7 +4889,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -5144,7 +4897,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -5152,7 +4905,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -5166,27 +4919,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -5194,7 +4949,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -5202,31 +4957,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -5234,7 +4989,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -5242,7 +4997,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -5250,13 +5005,13 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -5264,7 +5019,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="310.5">
+    <row r="12" ht="331.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -5272,7 +5027,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -5280,7 +5035,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -5288,7 +5043,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -5296,7 +5051,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -5310,631 +5065,633 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="36" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="4.75" style="39" customWidth="1"/>
-    <col min="3" max="4" width="12.75" style="39" customWidth="1"/>
-    <col min="5" max="6" width="8.75" style="39" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="39" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="39" customWidth="1"/>
-    <col min="9" max="9" width="23.625" style="39" customWidth="1"/>
-    <col min="10" max="10" width="46.5" style="39" customWidth="1"/>
-    <col min="11" max="32" width="9" style="39"/>
-    <col min="33" max="16384" width="23.375" style="39"/>
+    <col min="1" max="2" width="4.75" style="36" customWidth="1"/>
+    <col min="3" max="4" width="12.75" style="36" customWidth="1"/>
+    <col min="5" max="6" width="8.75" style="36" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="36" customWidth="1"/>
+    <col min="8" max="8" width="11.1296296296296" style="36" customWidth="1"/>
+    <col min="9" max="9" width="23.6296296296296" style="36" customWidth="1"/>
+    <col min="10" max="10" width="46.5" style="36" customWidth="1"/>
+    <col min="11" max="32" width="9" style="36"/>
+    <col min="33" max="16384" width="23.3796296296296" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1">
-      <c r="A1" s="40" t="s">
+    <row r="1" customHeight="1" spans="1:10">
+      <c r="A1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" s="38" customFormat="1" ht="33" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" s="35" customFormat="1" ht="33" customHeight="1" spans="1:10">
+      <c r="A2" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="42" t="s">
+      <c r="J2" s="39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="36" customHeight="1">
-      <c r="A3" s="43" t="s">
+    <row r="3" customHeight="1" spans="1:10">
+      <c r="A3" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="36" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="36" customHeight="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="77" t="s">
+    <row r="4" customHeight="1" spans="1:10">
+      <c r="A4" s="40"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="39" t="s">
+      <c r="J4" s="36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
-      <c r="A5" s="43"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="77" t="s">
+    <row r="5" customHeight="1" spans="1:10">
+      <c r="A5" s="40"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="36" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="36" customHeight="1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="77" t="s">
+    <row r="6" customHeight="1" spans="1:10">
+      <c r="A6" s="40"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="36" customHeight="1">
-      <c r="A7" s="43"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="76" t="s">
+    <row r="7" customHeight="1" spans="1:10">
+      <c r="A7" s="40"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="77" t="s">
+      <c r="H7" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="46" t="s">
+      <c r="J7" s="43" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="36" customHeight="1">
-      <c r="A8" s="43"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="77" t="s">
+    <row r="8" customHeight="1" spans="1:10">
+      <c r="A8" s="40"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I8" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="36" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="36" customHeight="1">
-      <c r="A9" s="43"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="77" t="s">
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="A9" s="40"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="36" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="36" customHeight="1">
-      <c r="A10" s="43"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="77" t="s">
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="A10" s="40"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="39" t="s">
+      <c r="J10" s="36" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="36" customHeight="1">
-      <c r="A11" s="43"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="76" t="s">
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="A11" s="40"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="76" t="s">
+      <c r="H11" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="36" customHeight="1">
-      <c r="A12" s="43"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="76" t="s">
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="A12" s="40"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="36" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="36" customHeight="1">
-      <c r="A13" s="43"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="76" t="s">
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="40"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="36" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="32" customHeight="1">
-      <c r="A14" s="43"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="76" t="s">
+    <row r="14" ht="32" customHeight="1" spans="1:10">
+      <c r="A14" s="40"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="39" t="s">
+      <c r="J14" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="36" customHeight="1">
-      <c r="A15" s="43"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="75" t="s">
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="A15" s="40"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="76" t="s">
+      <c r="H15" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="J15" s="39" t="s">
+      <c r="J15" s="36" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="36" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="76" t="s">
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="A16" s="40"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="73" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="J16" s="39" t="s">
+      <c r="J16" s="36" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="36" customHeight="1">
-      <c r="A17" s="43"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="76" t="s">
+    <row r="17" customHeight="1" spans="1:10">
+      <c r="A17" s="40"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I17" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="36" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="36" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="76" t="s">
+    <row r="18" customHeight="1" spans="1:10">
+      <c r="A18" s="40"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="36" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="36" customHeight="1">
-      <c r="A19" s="43"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="76" t="s">
+    <row r="19" customHeight="1" spans="1:10">
+      <c r="A19" s="40"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="G19" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="78" t="s">
+      <c r="H19" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="J19" s="48" t="s">
+      <c r="J19" s="45" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="36" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="78" t="s">
+    <row r="20" customHeight="1" spans="1:10">
+      <c r="A20" s="40"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="J20" s="48" t="s">
+      <c r="J20" s="45" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="36" customHeight="1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="78" t="s">
+    <row r="21" customHeight="1" spans="1:10">
+      <c r="A21" s="40"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="I21" s="49" t="s">
+      <c r="I21" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="J21" s="48" t="s">
+      <c r="J21" s="45" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="36" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="78" t="s">
+    <row r="22" customHeight="1" spans="1:10">
+      <c r="A22" s="40"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="I22" s="49" t="s">
+      <c r="I22" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="J22" s="48" t="s">
+      <c r="J22" s="45" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="36" customHeight="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="51" t="s">
+    <row r="23" customHeight="1" spans="1:10">
+      <c r="A23" s="40"/>
+      <c r="B23" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="54" t="s">
+      <c r="E23" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="G23" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="48" t="s">
+      <c r="H23" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="I23" s="49" t="s">
+      <c r="I23" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="J23" s="48" t="s">
+      <c r="J23" s="45" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="22.5">
-      <c r="A24" s="43"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="48" t="s">
+    <row r="24" ht="21.6" spans="1:10">
+      <c r="A24" s="40"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="I24" s="49" t="s">
+      <c r="I24" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="J24" s="49" t="s">
+      <c r="J24" s="46" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="22.5">
-      <c r="A25" s="43"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48" t="s">
+    <row r="25" ht="21.6" spans="1:10">
+      <c r="A25" s="40"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="I25" s="49" t="s">
+      <c r="I25" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="J25" s="48" t="s">
+      <c r="J25" s="45" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="13.5">
-      <c r="A26" s="43"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48" t="s">
+    <row r="26" ht="21.6" spans="1:10">
+      <c r="A26" s="40"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="I26" s="56" t="s">
+      <c r="I26" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="J26" s="48" t="s">
+      <c r="J26" s="45" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="13.5">
-      <c r="A27" s="43"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="53" t="s">
+    <row r="27" ht="21.6" spans="1:10">
+      <c r="A27" s="40"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="54" t="s">
+      <c r="E27" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="53" t="s">
+      <c r="F27" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="G27" s="57" t="s">
+      <c r="G27" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="H27" s="58" t="s">
+      <c r="H27" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="J27" s="49" t="s">
+      <c r="J27" s="46" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="22.5">
-      <c r="A28" s="43"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="79" t="s">
+    <row r="28" ht="21.6" spans="1:10">
+      <c r="A28" s="40"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="I28" s="49" t="s">
+      <c r="I28" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="J28" s="49" t="s">
+      <c r="J28" s="46" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="13.5">
-      <c r="A29" s="43"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="48" t="s">
+    <row r="29" ht="21.6" spans="1:10">
+      <c r="A29" s="40"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="I29" s="59" t="s">
+      <c r="I29" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="J29" s="60" t="s">
+      <c r="J29" s="57" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="13.5">
-      <c r="A30" s="43"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="64" t="s">
+    <row r="30" ht="21.6" spans="1:10">
+      <c r="A30" s="40"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="I30" s="56" t="s">
+      <c r="I30" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="J30" s="56" t="s">
+      <c r="J30" s="53" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5976,27 +5733,29 @@
     <hyperlink ref="H30" location="'0403030101针对特种设备行业领域的应用软件巡检服务'!A1" display="0403030104"/>
   </hyperlinks>
   <pageMargins left="0.118055555555556" right="0.118055555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -6004,7 +5763,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -6012,31 +5771,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -6044,7 +5803,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -6052,7 +5811,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -6060,13 +5819,13 @@
         <v>258</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -6074,7 +5833,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="310.5">
+    <row r="12" ht="331.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -6082,7 +5841,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -6090,7 +5849,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -6098,7 +5857,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -6106,7 +5865,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -6120,27 +5879,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -6148,7 +5909,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -6156,31 +5917,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -6188,7 +5949,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -6196,7 +5957,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -6204,13 +5965,13 @@
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -6218,7 +5979,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="310.5">
+    <row r="12" ht="331.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -6226,7 +5987,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -6234,7 +5995,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -6242,7 +6003,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -6250,7 +6011,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -6264,27 +6025,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -6292,7 +6055,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -6300,31 +6063,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -6332,7 +6095,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -6340,7 +6103,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -6348,13 +6111,13 @@
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="40.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" ht="43.2" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -6362,7 +6125,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="378">
+    <row r="12" ht="403.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -6370,7 +6133,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -6378,7 +6141,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -6386,7 +6149,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -6394,7 +6157,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -6408,27 +6171,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="2" max="2" width="68.75" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="20"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="19"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -6436,7 +6201,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -6444,31 +6209,31 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="79" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="80" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>152</v>
       </c>
@@ -6476,7 +6241,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
@@ -6484,7 +6249,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="13.5">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>154</v>
       </c>
@@ -6492,13 +6257,13 @@
         <v>274</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="21"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="20"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -6506,15 +6271,15 @@
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="270">
-      <c r="A12" s="23" t="s">
+    <row r="12" ht="288" spans="1:2">
+      <c r="A12" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -6522,7 +6287,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -6530,7 +6295,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -6538,7 +6303,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -6552,27 +6317,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="1" max="1" width="15.8796296296296" customWidth="1"/>
     <col min="2" max="2" width="68.75" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B1" s="20"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="19"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -6580,7 +6347,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -6588,31 +6355,31 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="79" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="80" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>152</v>
       </c>
@@ -6620,7 +6387,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
@@ -6628,7 +6395,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="13.5">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>154</v>
       </c>
@@ -6636,13 +6403,13 @@
         <v>279</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="21"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="20"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -6650,15 +6417,15 @@
         <v>275</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="135">
-      <c r="A12" s="23" t="s">
+    <row r="12" ht="144" spans="1:2">
+      <c r="A12" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -6666,7 +6433,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -6674,7 +6441,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -6682,7 +6449,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -6696,27 +6463,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="16.75" customWidth="1"/>
     <col min="2" max="2" width="68.75" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="20"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="19"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -6724,7 +6493,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -6732,31 +6501,31 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="79" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="80" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>152</v>
       </c>
@@ -6764,7 +6533,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
@@ -6772,7 +6541,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="13.5">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>154</v>
       </c>
@@ -6780,13 +6549,13 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="21"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="20"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -6794,7 +6563,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="216">
+    <row r="12" ht="230.4" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
@@ -6802,7 +6571,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -6810,7 +6579,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -6818,7 +6587,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -6826,7 +6595,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -6840,27 +6609,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
     <col min="2" max="2" width="68.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
+    <row r="1" spans="1:2">
       <c r="A1" s="12" t="s">
         <v>289</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="13.5">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -6868,7 +6639,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -6876,23 +6647,23 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="81" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
@@ -6900,7 +6671,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -6908,7 +6679,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>291</v>
       </c>
@@ -6916,7 +6687,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>292</v>
       </c>
@@ -6924,21 +6695,21 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
+    <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="13.5">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="9" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="81">
+    <row r="12" ht="100.8" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
@@ -6946,7 +6717,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -6954,7 +6725,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -6962,7 +6733,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -6970,7 +6741,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -6984,27 +6755,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
     <col min="2" max="2" width="60.75" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="82" t="s">
         <v>298</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="13.5">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -7012,7 +6785,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -7020,23 +6793,23 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="83" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="84" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
@@ -7044,7 +6817,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>152</v>
       </c>
@@ -7052,7 +6825,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
@@ -7060,7 +6833,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>154</v>
       </c>
@@ -7068,13 +6841,13 @@
         <v>302</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
+    <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="13.5">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -7082,7 +6855,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="243">
+    <row r="12" ht="259.2" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
@@ -7090,7 +6863,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" ht="28.8" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -7098,7 +6871,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -7106,7 +6879,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -7114,7 +6887,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -7128,27 +6901,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
     <col min="2" max="2" width="62.25" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="82" t="s">
         <v>306</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="13.5">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -7156,7 +6931,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -7164,23 +6939,23 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="83" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
@@ -7188,7 +6963,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>152</v>
       </c>
@@ -7196,7 +6971,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>153</v>
       </c>
@@ -7204,7 +6979,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>154</v>
       </c>
@@ -7212,13 +6987,13 @@
         <v>309</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
+    <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="14.25">
+    <row r="11" ht="15.6" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -7226,7 +7001,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="216">
+    <row r="12" ht="230.4" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
@@ -7234,7 +7009,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>311</v>
       </c>
@@ -7242,7 +7017,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -7250,7 +7025,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -7258,7 +7033,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -7272,27 +7047,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="64.875" customWidth="1"/>
+    <col min="2" max="2" width="64.8796296296296" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
+    <row r="1" spans="1:2">
       <c r="A1" s="12" t="s">
         <v>313</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="13.5">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -7300,7 +7077,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -7308,23 +7085,23 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="83" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
@@ -7332,7 +7109,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -7340,7 +7117,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>291</v>
       </c>
@@ -7348,7 +7125,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>292</v>
       </c>
@@ -7356,13 +7133,13 @@
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
+    <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="13.5">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -7370,7 +7147,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="202.5">
+    <row r="12" ht="216" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
@@ -7378,7 +7155,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -7386,7 +7163,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -7394,7 +7171,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -7402,7 +7179,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
@@ -7416,26 +7193,28 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="68.775" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="68.7777777777778" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="16384" width="68.75" style="24" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="16384" width="68.75" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -7443,7 +7222,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -7451,31 +7230,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -7483,7 +7262,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -7491,7 +7270,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -7499,13 +7278,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="36" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="37"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -7513,7 +7292,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="216">
+    <row r="12" ht="230.4" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -7521,7 +7300,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -7529,7 +7308,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -7537,7 +7316,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -7545,7 +7324,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -7559,27 +7338,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="10.8796296296296" customWidth="1"/>
     <col min="2" max="2" width="68.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="13.5">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -7587,7 +7368,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
@@ -7595,23 +7376,23 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="83" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
@@ -7619,7 +7400,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -7627,29 +7408,29 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>291</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="27">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>292</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="13.5">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" ht="13.5">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>157</v>
       </c>
@@ -7657,15 +7438,15 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="81">
+    <row r="12" ht="100.8" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>159</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="13.5">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>161</v>
       </c>
@@ -7673,7 +7454,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>163</v>
       </c>
@@ -7681,7 +7462,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>165</v>
       </c>
@@ -7689,12 +7470,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -7703,26 +7484,28 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="68.775" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="68.7777777777778" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="16384" width="68.75" style="24" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="16384" width="68.75" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -7730,7 +7513,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -7738,31 +7521,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -7770,7 +7553,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -7778,7 +7561,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -7786,13 +7569,13 @@
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -7800,7 +7583,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="243">
+    <row r="12" ht="259.2" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -7808,7 +7591,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -7816,7 +7599,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -7824,7 +7607,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -7832,7 +7615,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -7846,141 +7629,143 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="68.775" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="68.7777777777778" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="17.5" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="29" customWidth="1"/>
-    <col min="3" max="16384" width="68.75" style="24" customWidth="1"/>
+    <col min="1" max="1" width="17.5" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="28" customWidth="1"/>
+    <col min="3" max="16384" width="68.75" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="33"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
-      <c r="A2" s="34" t="s">
+      <c r="B1" s="32"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
-      <c r="A4" s="34" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="78" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="78" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
-      <c r="A6" s="34" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="78" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
-      <c r="A7" s="34" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
-      <c r="A8" s="34" t="s">
+    <row r="8" ht="28.8" spans="1:2">
+      <c r="A8" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
-      <c r="A9" s="34" t="s">
+    <row r="9" ht="28.8" spans="1:2">
+      <c r="A9" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="35" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="35"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
-      <c r="A11" s="34" t="s">
+      <c r="B10" s="34"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="202.5">
-      <c r="A12" s="34" t="s">
+    <row r="12" ht="216" spans="1:2">
+      <c r="A12" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
-      <c r="A14" s="34" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="30" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
-      <c r="A16" s="34" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="30" t="s">
         <v>180</v>
       </c>
     </row>
@@ -7990,141 +7775,143 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="68.8916666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="68.8888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="29" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="29" customWidth="1"/>
-    <col min="3" max="16384" width="68.875" style="29" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="28" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="28" customWidth="1"/>
+    <col min="3" max="16384" width="68.8796296296296" style="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="30"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
-      <c r="A2" s="31" t="s">
+      <c r="B1" s="29"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="78" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="78" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="78" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
-      <c r="A8" s="31" t="s">
+    <row r="8" ht="28.8" spans="1:2">
+      <c r="A8" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
-      <c r="A9" s="31" t="s">
+    <row r="9" ht="28.8" spans="1:2">
+      <c r="A9" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="32" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="32"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
-      <c r="A11" s="31" t="s">
+      <c r="B10" s="31"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="270">
-      <c r="A12" s="31" t="s">
+    <row r="12" ht="288" spans="1:2">
+      <c r="A12" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="30" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
-      <c r="A16" s="31" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="30" t="s">
         <v>184</v>
       </c>
     </row>
@@ -8134,27 +7921,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -8162,7 +7951,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -8170,31 +7959,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -8202,7 +7991,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -8210,7 +7999,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -8218,13 +8007,13 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -8232,7 +8021,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="270">
+    <row r="12" ht="288" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -8240,7 +8029,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -8248,7 +8037,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -8256,7 +8045,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -8264,7 +8053,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -8278,27 +8067,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -8306,7 +8097,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -8314,31 +8105,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -8346,7 +8137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -8354,7 +8145,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -8362,13 +8153,13 @@
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -8376,7 +8167,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="270">
+    <row r="12" ht="288" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -8384,7 +8175,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -8392,7 +8183,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -8400,7 +8191,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -8408,7 +8199,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -8422,27 +8213,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.75" style="24" customWidth="1"/>
-    <col min="2" max="2" width="68.75" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="24"/>
+    <col min="1" max="1" width="15.75" style="23" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="8.87962962962963" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="26"/>
-    </row>
-    <row r="2" spans="1:2" ht="13.5">
+      <c r="B1" s="25"/>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
         <v>143</v>
       </c>
@@ -8450,7 +8243,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.5">
+    <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
         <v>145</v>
       </c>
@@ -8458,31 +8251,31 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.5">
+    <row r="4" spans="1:2">
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="77" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="77" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.5">
+    <row r="6" spans="1:2">
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="77" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.5">
+    <row r="7" spans="1:2">
       <c r="A7" s="16" t="s">
         <v>152</v>
       </c>
@@ -8490,7 +8283,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="16" t="s">
         <v>153</v>
       </c>
@@ -8498,7 +8291,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="16" t="s">
         <v>154</v>
       </c>
@@ -8506,13 +8299,13 @@
         <v>197</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.5">
-      <c r="A10" s="27" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="28"/>
-    </row>
-    <row r="11" spans="1:2" ht="13.5">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
         <v>157</v>
       </c>
@@ -8520,7 +8313,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="270">
+    <row r="12" ht="288" spans="1:2">
       <c r="A12" s="16" t="s">
         <v>159</v>
       </c>
@@ -8528,7 +8321,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.5">
+    <row r="13" spans="1:2">
       <c r="A13" s="16" t="s">
         <v>161</v>
       </c>
@@ -8536,7 +8329,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="13.5">
+    <row r="14" spans="1:2">
       <c r="A14" s="16" t="s">
         <v>163</v>
       </c>
@@ -8544,7 +8337,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="13.5">
+    <row r="15" spans="1:2">
       <c r="A15" s="16" t="s">
         <v>165</v>
       </c>
@@ -8552,7 +8345,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="13.5">
+    <row r="16" spans="1:2">
       <c r="A16" s="16" t="s">
         <v>167</v>
       </c>
@@ -8566,6 +8359,7 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/1-运维服务目录/TXHS-01-02-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/TXHS-01-02-组织级运维服务目录.xlsx
@@ -2008,38 +2008,45 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2076,13 +2083,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2627,7 +2627,7 @@
     </border>
   </borders>
   <cellStyleXfs count="62">
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
@@ -2706,7 +2706,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2822,112 +2822,118 @@
     <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -3331,113 +3337,113 @@
   <sheetData>
     <row r="1" ht="14.1" customHeight="1"/>
     <row r="3" spans="1:9">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
     </row>
     <row r="5" ht="27" customHeight="1" spans="1:9">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:9">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="65" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="65" t="s">
+      <c r="F7" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
     </row>
     <row r="9" ht="21" customHeight="1" spans="1:9">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="68" t="s">
+      <c r="D10" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="68" t="s">
+      <c r="E10" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="68" t="s">
+      <c r="G10" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="68" t="s">
+      <c r="H10" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="69"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
       <c r="I11" t="s">
         <v>13</v>
       </c>
@@ -3446,32 +3452,32 @@
       <c r="A12" s="23">
         <v>1</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="71" t="s">
+      <c r="G12" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="71" t="s">
+      <c r="H12" s="73" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" ht="30.9" customHeight="1" spans="1:9">
       <c r="A13" s="23"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
@@ -3519,76 +3525,76 @@
       <c r="H17" s="23"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3647,7 +3653,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3655,7 +3661,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3663,7 +3669,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3793,7 +3799,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3801,7 +3807,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3809,7 +3815,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3939,7 +3945,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3947,7 +3953,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3955,7 +3961,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4085,7 +4091,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4093,7 +4099,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4101,7 +4107,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4231,7 +4237,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4239,7 +4245,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4247,7 +4253,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4377,7 +4383,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4385,7 +4391,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4393,7 +4399,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4523,7 +4529,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4531,7 +4537,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4539,7 +4545,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>86</v>
       </c>
     </row>
@@ -4669,7 +4675,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4677,7 +4683,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4685,7 +4691,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4815,7 +4821,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4823,7 +4829,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4831,7 +4837,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4961,7 +4967,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4969,7 +4975,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>251</v>
       </c>
     </row>
@@ -4977,7 +4983,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>97</v>
       </c>
     </row>
@@ -5137,561 +5143,561 @@
       <c r="A3" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="74" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="74" t="s">
+      <c r="H3" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="43" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="40"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="74" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="43" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="40"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="74" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="40"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="74" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="45" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:10">
       <c r="A7" s="40"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="73" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="45" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="40"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="74" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="43" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="40"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="74" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="43" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="40"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="74" t="s">
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="I10" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="36" t="s">
+      <c r="J10" s="43" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="40"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="73" t="s">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="73" t="s">
+      <c r="F11" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="73" t="s">
+      <c r="H11" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="36" t="s">
+      <c r="J11" s="43" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="40"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="73" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="43" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="40"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="73" t="s">
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="I13" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="36" t="s">
+      <c r="J13" s="43" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:10">
       <c r="A14" s="40"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="73" t="s">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="36" t="s">
+      <c r="I14" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="36" t="s">
+      <c r="J14" s="43" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:10">
       <c r="A15" s="40"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="72" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="74" t="s">
         <v>79</v>
       </c>
       <c r="E15" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="73" t="s">
+      <c r="H15" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="I15" s="36" t="s">
+      <c r="I15" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="43" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:10">
       <c r="A16" s="40"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="73" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="36" t="s">
+      <c r="I16" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="J16" s="36" t="s">
+      <c r="J16" s="43" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:10">
       <c r="A17" s="40"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="73" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="I17" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="J17" s="36" t="s">
+      <c r="J17" s="43" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:10">
       <c r="A18" s="40"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="73" t="s">
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="I18" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="J18" s="43" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:10">
       <c r="A19" s="40"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="73" t="s">
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G19" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="H19" s="75" t="s">
+      <c r="H19" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="I19" s="46" t="s">
+      <c r="I19" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="J19" s="45" t="s">
+      <c r="J19" s="47" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:10">
       <c r="A20" s="40"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="75" t="s">
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="46" t="s">
+      <c r="I20" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="J20" s="45" t="s">
+      <c r="J20" s="47" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:10">
       <c r="A21" s="40"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="75" t="s">
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="I21" s="46" t="s">
+      <c r="I21" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="J21" s="45" t="s">
+      <c r="J21" s="47" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:10">
       <c r="A22" s="40"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="75" t="s">
+      <c r="B22" s="49"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="I22" s="46" t="s">
+      <c r="I22" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="J22" s="45" t="s">
+      <c r="J22" s="47" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:10">
       <c r="A23" s="40"/>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="E23" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="I23" s="46" t="s">
+      <c r="I23" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="J23" s="45" t="s">
+      <c r="J23" s="47" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" ht="21.6" spans="1:10">
+    <row r="24" ht="19.2" spans="1:10">
       <c r="A24" s="40"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="45" t="s">
+      <c r="B24" s="50"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="I24" s="46" t="s">
+      <c r="I24" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="J24" s="46" t="s">
+      <c r="J24" s="48" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" ht="21.6" spans="1:10">
+    <row r="25" ht="26" customHeight="1" spans="1:10">
       <c r="A25" s="40"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="45" t="s">
+      <c r="B25" s="50"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="I25" s="46" t="s">
+      <c r="I25" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="J25" s="45" t="s">
+      <c r="J25" s="47" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" ht="21.6" spans="1:10">
+    <row r="26" ht="25" customHeight="1" spans="1:10">
       <c r="A26" s="40"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="45" t="s">
+      <c r="B26" s="50"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="I26" s="53" t="s">
+      <c r="I26" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="J26" s="45" t="s">
+      <c r="J26" s="47" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" ht="21.6" spans="1:10">
+    <row r="27" ht="14.4" spans="1:10">
       <c r="A27" s="40"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="50" t="s">
+      <c r="B27" s="50"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="E27" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="G27" s="54" t="s">
+      <c r="G27" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="H27" s="55" t="s">
+      <c r="H27" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="I27" s="46" t="s">
+      <c r="I27" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="J27" s="46" t="s">
+      <c r="J27" s="48" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" ht="21.6" spans="1:10">
+    <row r="28" ht="23" customHeight="1" spans="1:10">
       <c r="A28" s="40"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="76" t="s">
+      <c r="B28" s="50"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="I28" s="46" t="s">
+      <c r="I28" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="J28" s="46" t="s">
+      <c r="J28" s="48" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" ht="21.6" spans="1:10">
+    <row r="29" ht="14.4" spans="1:10">
       <c r="A29" s="40"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="45" t="s">
+      <c r="B29" s="50"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="I29" s="56" t="s">
+      <c r="I29" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="59" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" ht="21.6" spans="1:10">
+    <row r="30" ht="14.4" spans="1:10">
       <c r="A30" s="40"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="61" t="s">
+      <c r="B30" s="50"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="I30" s="53" t="s">
+      <c r="I30" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="J30" s="53" t="s">
+      <c r="J30" s="55" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5775,7 +5781,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5783,7 +5789,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>251</v>
       </c>
     </row>
@@ -5791,7 +5797,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5921,7 +5927,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5929,7 +5935,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>251</v>
       </c>
     </row>
@@ -5937,7 +5943,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>103</v>
       </c>
     </row>
@@ -6067,7 +6073,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>225</v>
       </c>
     </row>
@@ -6075,7 +6081,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>251</v>
       </c>
     </row>
@@ -6083,7 +6089,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6213,7 +6219,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="81" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6221,7 +6227,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>272</v>
       </c>
     </row>
@@ -6229,7 +6235,7 @@
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="82" t="s">
         <v>115</v>
       </c>
     </row>
@@ -6359,7 +6365,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="81" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6367,7 +6373,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>272</v>
       </c>
     </row>
@@ -6375,7 +6381,7 @@
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="82" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6505,7 +6511,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="81" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6513,7 +6519,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>272</v>
       </c>
     </row>
@@ -6521,7 +6527,7 @@
       <c r="A6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="82" t="s">
         <v>121</v>
       </c>
     </row>
@@ -6651,7 +6657,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="83" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6659,7 +6665,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>272</v>
       </c>
     </row>
@@ -6772,7 +6778,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>298</v>
       </c>
       <c r="B1" s="3"/>
@@ -6797,7 +6803,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="85" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6805,7 +6811,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="86" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6918,7 +6924,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="84" t="s">
         <v>306</v>
       </c>
       <c r="B1" s="3"/>
@@ -6943,7 +6949,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="85" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6951,7 +6957,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>307</v>
       </c>
     </row>
@@ -7089,7 +7095,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="85" t="s">
         <v>299</v>
       </c>
     </row>
@@ -7097,7 +7103,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>307</v>
       </c>
     </row>
@@ -7234,7 +7240,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7242,7 +7248,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7250,7 +7256,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>37</v>
       </c>
     </row>
@@ -7380,7 +7386,7 @@
       <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="85" t="s">
         <v>299</v>
       </c>
     </row>
@@ -7388,7 +7394,7 @@
       <c r="A5" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="82" t="s">
         <v>307</v>
       </c>
     </row>
@@ -7525,7 +7531,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7533,7 +7539,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7541,7 +7547,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>40</v>
       </c>
     </row>
@@ -7671,7 +7677,7 @@
       <c r="A4" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="80" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7679,7 +7685,7 @@
       <c r="A5" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="80" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7687,7 +7693,7 @@
       <c r="A6" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="80" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7817,7 +7823,7 @@
       <c r="A4" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="80" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7825,7 +7831,7 @@
       <c r="A5" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="80" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7833,7 +7839,7 @@
       <c r="A6" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="80" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7963,7 +7969,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7971,7 +7977,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>186</v>
       </c>
     </row>
@@ -7979,7 +7985,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8109,7 +8115,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8117,7 +8123,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>186</v>
       </c>
     </row>
@@ -8125,7 +8131,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>54</v>
       </c>
     </row>
@@ -8255,7 +8261,7 @@
       <c r="A4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="79" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8263,7 +8269,7 @@
       <c r="A5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="79" t="s">
         <v>186</v>
       </c>
     </row>
@@ -8271,7 +8277,7 @@
       <c r="A6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="79" t="s">
         <v>57</v>
       </c>
     </row>
